--- a/artfynd/A 64364-2023 artfynd.xlsx
+++ b/artfynd/A 64364-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133510529</v>
       </c>
       <c r="B2" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 64364-2023 artfynd.xlsx
+++ b/artfynd/A 64364-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133510529</v>
       </c>
       <c r="B2" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 64364-2023 artfynd.xlsx
+++ b/artfynd/A 64364-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133510529</v>
       </c>
       <c r="B2" t="n">
-        <v>98005</v>
+        <v>98033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 64364-2023 artfynd.xlsx
+++ b/artfynd/A 64364-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133510529</v>
       </c>
       <c r="B2" t="n">
-        <v>98033</v>
+        <v>98043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 64364-2023 artfynd.xlsx
+++ b/artfynd/A 64364-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133510529</v>
       </c>
       <c r="B2" t="n">
-        <v>98043</v>
+        <v>98045</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 64364-2023 artfynd.xlsx
+++ b/artfynd/A 64364-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133510529</v>
       </c>
       <c r="B2" t="n">
-        <v>98046</v>
+        <v>98060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
